--- a/data/trans_dic/P17A-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P17A-Habitat-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>17,48%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,56%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>15,36; 21,13</t>
+          <t>15,26; 21,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>21,79; 28,85</t>
+          <t>22,32; 29,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>25,29; 32,26</t>
+          <t>25,14; 32,28</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15,07; 20,74</t>
+          <t>14,88; 20,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>28,05; 35,01</t>
+          <t>27,71; 34,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,72; 38,09</t>
+          <t>30,42; 37,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>33,04; 40,68</t>
+          <t>33,19; 40,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>22,5; 28,1</t>
+          <t>21,82; 27,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>22,48; 27,11</t>
+          <t>22,57; 27,02</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>27,42; 32,64</t>
+          <t>27,6; 32,54</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>30,16; 35,58</t>
+          <t>30,36; 35,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>19,54; 23,6</t>
+          <t>19,29; 23,29</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>21,23%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>17,36; 22,62</t>
+          <t>17,42; 22,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,69; 26,26</t>
+          <t>20,78; 26,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,68; 29,45</t>
+          <t>23,18; 29,15</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 20,25</t>
+          <t>16,9; 22,15</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>28,64; 34,68</t>
+          <t>28,85; 34,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,72; 37,62</t>
+          <t>31,32; 37,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,79; 36,82</t>
+          <t>30,93; 37,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>20,26; 24,97</t>
+          <t>20,7; 25,2</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>24,08; 27,96</t>
+          <t>23,99; 28,09</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>26,93; 31,19</t>
+          <t>26,92; 31,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>28,06; 32,23</t>
+          <t>28,17; 32,45</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,25; 21,86</t>
+          <t>19,56; 23,17</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>22,13%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>20,2%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,44; 25,23</t>
+          <t>18,15; 24,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>20,08; 26,98</t>
+          <t>20,21; 26,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,22; 26,34</t>
+          <t>20,18; 26,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,91; 22,57</t>
+          <t>15,48; 21,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>25,91; 32,62</t>
+          <t>25,9; 32,53</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,36; 33,0</t>
+          <t>26,55; 33,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,73; 35,45</t>
+          <t>28,75; 35,59</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,99; 21,58</t>
+          <t>19,7; 24,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22,92; 27,65</t>
+          <t>22,99; 27,69</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24,16; 28,98</t>
+          <t>24,44; 29,38</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25,05; 30,05</t>
+          <t>25,08; 29,82</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,48; 20,41</t>
+          <t>18,32; 22,33</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>25,68%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>18,26; 23,32</t>
+          <t>18,45; 23,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>17,29; 22,81</t>
+          <t>17,41; 22,87</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20,68; 26,33</t>
+          <t>20,92; 26,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19,88; 26,03</t>
+          <t>19,53; 25,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 34,47</t>
+          <t>28,64; 34,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>28,82; 34,58</t>
+          <t>28,82; 34,62</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,76; 32,51</t>
+          <t>26,36; 32,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>27,94; 48,13</t>
+          <t>26,41; 31,45</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,58; 28,39</t>
+          <t>24,55; 28,56</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23,95; 28,15</t>
+          <t>23,99; 28,04</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>24,82; 28,9</t>
+          <t>24,76; 28,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,18; 37,52</t>
+          <t>23,93; 27,59</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>24,51%</t>
+          <t>24,84%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,43</t>
+          <t>18,79; 21,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>21,39; 24,38</t>
+          <t>21,36; 24,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,57; 26,71</t>
+          <t>23,88; 26,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,99; 20,61</t>
+          <t>18,19; 21,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>29,29; 32,43</t>
+          <t>29,46; 32,66</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,06; 34,22</t>
+          <t>30,99; 34,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,33; 34,63</t>
+          <t>31,38; 34,35</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>20,74; 28,71</t>
+          <t>23,62; 26,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>24,69; 26,78</t>
+          <t>24,59; 26,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,86; 28,95</t>
+          <t>26,72; 28,89</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,98; 30,13</t>
+          <t>28,02; 30,26</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>19,04; 24,15</t>
+          <t>21,32; 23,19</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113108</t>
+          <t>120760</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>168083</t>
+          <t>179816</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>281191</t>
+          <t>300575</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>106599; 146620</t>
+          <t>105934; 147811</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>153105; 202633</t>
+          <t>156769; 204993</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>170678; 217713</t>
+          <t>169643; 217856</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>95770; 131782</t>
+          <t>102778; 142870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>193109; 240959</t>
+          <t>190767; 238268</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>213006; 264106</t>
+          <t>210958; 261445</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>222273; 273711</t>
+          <t>223297; 274071</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>151805; 189566</t>
+          <t>159763; 198423</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>310797; 374763</t>
+          <t>311942; 373481</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>382761; 455600</t>
+          <t>385226; 454271</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>406502; 479473</t>
+          <t>409138; 478645</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>256031; 309128</t>
+          <t>274499; 331366</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184235</t>
+          <t>204293</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>217045</t>
+          <t>245527</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>401280</t>
+          <t>449820</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>166946; 217565</t>
+          <t>167540; 219975</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>210382; 267027</t>
+          <t>211300; 265311</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>242143; 301121</t>
+          <t>237001; 298033</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88089; 241543</t>
+          <t>177298; 232376</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>277031; 335453</t>
+          <t>279100; 337567</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>327401; 388319</t>
+          <t>323290; 385179</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>321139; 383973</t>
+          <t>322567; 385828</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>193975; 238992</t>
+          <t>221504; 269596</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>464538; 539488</t>
+          <t>462804; 541890</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>551749; 638991</t>
+          <t>551571; 638177</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>579495; 665601</t>
+          <t>581766; 670195</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>263311; 470108</t>
+          <t>414441; 490928</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>133665</t>
+          <t>146333</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>148782</t>
+          <t>179754</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>282447</t>
+          <t>326086</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>124945; 170962</t>
+          <t>122949; 168215</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>150958; 202804</t>
+          <t>151927; 201978</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>153561; 200091</t>
+          <t>153313; 199937</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112014; 158862</t>
+          <t>124187; 172116</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>177178; 223070</t>
+          <t>177091; 222450</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>204574; 256097</t>
+          <t>206061; 258631</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>225523; 278296</t>
+          <t>225657; 279404</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>74592; 201413</t>
+          <t>160020; 202249</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>312038; 376452</t>
+          <t>312928; 376967</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>369096; 442683</t>
+          <t>373441; 448821</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>386887; 464124</t>
+          <t>387410; 460573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>188017; 334119</t>
+          <t>295694; 360473</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210347</t>
+          <t>219239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>362652</t>
+          <t>321523</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>572999</t>
+          <t>540763</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>171763; 219309</t>
+          <t>173560; 222854</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>162866; 214855</t>
+          <t>164032; 215371</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>193930; 246881</t>
+          <t>196138; 245906</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>184085; 241048</t>
+          <t>193266; 248096</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>296290; 357617</t>
+          <t>297210; 357369</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>301366; 361548</t>
+          <t>301299; 361971</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>279358; 339312</t>
+          <t>275113; 341546</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>305556; 526213</t>
+          <t>294793; 351145</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>486163; 561621</t>
+          <t>485564; 564943</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475970; 559435</t>
+          <t>476797; 557369</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>491779; 572657</t>
+          <t>490491; 569662</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>508477; 757823</t>
+          <t>503895; 580961</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>641355</t>
+          <t>690624</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>896562</t>
+          <t>926620</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1537917</t>
+          <t>1617244</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>610391; 701611</t>
+          <t>615137; 706471</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>730173; 831885</t>
+          <t>728996; 833045</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>799914; 906779</t>
+          <t>810478; 907318</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>483831; 712631</t>
+          <t>642263; 746952</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>989297; 1095103</t>
+          <t>994968; 1102982</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1101719; 1213743</t>
+          <t>1099160; 1211669</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1110662; 1227594</t>
+          <t>1112386; 1217719</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>758693; 1050300</t>
+          <t>881086; 972095</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1642244; 1780854</t>
+          <t>1635480; 1776710</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1869143; 2015001</t>
+          <t>1859772; 2011120</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1941723; 2090482</t>
+          <t>1944005; 2099412</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1355095; 1718603</t>
+          <t>1547884; 1683892</t>
         </is>
       </c>
     </row>
